--- a/experiments/experiment_sheets/experiments_ls.xlsx
+++ b/experiments/experiment_sheets/experiments_ls.xlsx
@@ -61,7 +61,7 @@
     <t>H_ins</t>
   </si>
   <si>
-    <t>Δφ (100m)</t>
+    <t>Δφ (100)</t>
   </si>
 </sst>
 </file>
@@ -119,7 +119,7 @@
     <col min="7" max="7" width="13.7109375" customWidth="true"/>
     <col min="8" max="8" width="7.28515625" customWidth="true"/>
     <col min="9" max="9" width="6" customWidth="true"/>
-    <col min="10" max="10" width="13.42578125" customWidth="true"/>
+    <col min="10" max="10" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -183,7 +183,7 @@
         <v>25</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.59106891618354351</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="3">
@@ -215,7 +215,7 @@
         <v>50</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.59275792051984555</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="4">
@@ -247,7 +247,7 @@
         <v>25</v>
       </c>
       <c r="J4" s="0">
-        <v>-0.58811736324901609</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="5">
@@ -279,7 +279,7 @@
         <v>50</v>
       </c>
       <c r="J5" s="0">
-        <v>-0.58719181221792238</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="6">
@@ -311,7 +311,7 @@
         <v>25</v>
       </c>
       <c r="J6" s="0">
-        <v>-0.51804161566015861</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="7">
@@ -343,7 +343,7 @@
         <v>50</v>
       </c>
       <c r="J7" s="0">
-        <v>-0.52419001507311336</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="8">
@@ -375,7 +375,7 @@
         <v>25</v>
       </c>
       <c r="J8" s="0">
-        <v>-1.896785127711969</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="9">
@@ -407,7 +407,7 @@
         <v>50</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.56403586782312676</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="10">
@@ -439,7 +439,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="0">
-        <v>56.263253132020594</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="11">
@@ -471,7 +471,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="0">
-        <v>56.263249612801175</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="12">
@@ -503,7 +503,7 @@
         <v>2</v>
       </c>
       <c r="J12" s="0">
-        <v>96.834209716132534</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="13">
@@ -535,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="J13" s="0">
-        <v>96.834209097959075</v>
+        <v>220.56982464859516</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         <v>2</v>
       </c>
       <c r="J14" s="0">
-        <v>62.207934588245593</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="15">
@@ -599,7 +599,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="0">
-        <v>62.207937041536042</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="16">
@@ -631,7 +631,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="0">
-        <v>105.11739021826341</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
     <row r="17">
@@ -663,7 +663,7 @@
         <v>2</v>
       </c>
       <c r="J17" s="0">
-        <v>105.11739209548676</v>
+        <v>195.10251474120889</v>
       </c>
     </row>
   </sheetData>
